--- a/artfynd/A 20398-2024 artfynd.xlsx
+++ b/artfynd/A 20398-2024 artfynd.xlsx
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119525839</v>
+        <v>119528005</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90752</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,43 +2537,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657171</v>
+        <v>657098</v>
       </c>
       <c r="R18" t="n">
-        <v>7003519</v>
+        <v>7003930</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2600,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2610,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,10 +2637,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119528005</v>
+        <v>119523532</v>
       </c>
       <c r="B19" t="n">
-        <v>90752</v>
+        <v>57310</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,41 +2649,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657098</v>
+        <v>656779</v>
       </c>
       <c r="R19" t="n">
-        <v>7003930</v>
+        <v>7003525</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119523532</v>
+        <v>119525839</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656779</v>
+        <v>657171</v>
       </c>
       <c r="R20" t="n">
-        <v>7003525</v>
+        <v>7003519</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119527794</v>
+        <v>119528084</v>
       </c>
       <c r="B30" t="n">
-        <v>91005</v>
+        <v>91858</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,38 +3906,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>4368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657086</v>
+        <v>657148</v>
       </c>
       <c r="R30" t="n">
-        <v>7004011</v>
+        <v>7003847</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,22 +3994,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119528084</v>
+        <v>119527794</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>91005</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,38 +4018,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>1209</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657148</v>
+        <v>657086</v>
       </c>
       <c r="R31" t="n">
-        <v>7003847</v>
+        <v>7004011</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,12 +4106,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 20398-2024 artfynd.xlsx
+++ b/artfynd/A 20398-2024 artfynd.xlsx
@@ -2525,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119528005</v>
+        <v>119525839</v>
       </c>
       <c r="B18" t="n">
-        <v>90752</v>
+        <v>57310</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2537,38 +2537,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657098</v>
+        <v>657171</v>
       </c>
       <c r="R18" t="n">
-        <v>7003930</v>
+        <v>7003519</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,7 +2605,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2610,7 +2615,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2637,10 +2642,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119523532</v>
+        <v>119528005</v>
       </c>
       <c r="B19" t="n">
-        <v>57310</v>
+        <v>90752</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2649,46 +2654,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656779</v>
+        <v>657098</v>
       </c>
       <c r="R19" t="n">
-        <v>7003525</v>
+        <v>7003930</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,7 +2754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119525839</v>
+        <v>119523532</v>
       </c>
       <c r="B20" t="n">
         <v>57310</v>
@@ -2795,17 +2795,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>657171</v>
+        <v>656779</v>
       </c>
       <c r="R20" t="n">
-        <v>7003519</v>
+        <v>7003525</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3436,10 +3436,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119523806</v>
+        <v>119527614</v>
       </c>
       <c r="B26" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,38 +3448,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>656688</v>
+        <v>657068</v>
       </c>
       <c r="R26" t="n">
-        <v>7003344</v>
+        <v>7004042</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3511,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3521,7 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3548,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119528244</v>
+        <v>119523806</v>
       </c>
       <c r="B27" t="n">
         <v>100171</v>
@@ -3584,14 +3589,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656999</v>
+        <v>656688</v>
       </c>
       <c r="R27" t="n">
-        <v>7003725</v>
+        <v>7003344</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3628,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3633,7 +3638,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3660,10 +3665,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119527614</v>
+        <v>119528244</v>
       </c>
       <c r="B28" t="n">
-        <v>57310</v>
+        <v>100171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3672,43 +3677,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>657068</v>
+        <v>656999</v>
       </c>
       <c r="R28" t="n">
-        <v>7004042</v>
+        <v>7003725</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,7 +3740,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3894,10 +3894,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119528084</v>
+        <v>119527794</v>
       </c>
       <c r="B30" t="n">
-        <v>91858</v>
+        <v>91005</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,38 +3906,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4368</v>
+        <v>1209</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657148</v>
+        <v>657086</v>
       </c>
       <c r="R30" t="n">
-        <v>7003847</v>
+        <v>7004011</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3969,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3994,22 +3994,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119527794</v>
+        <v>119528084</v>
       </c>
       <c r="B31" t="n">
-        <v>91005</v>
+        <v>91858</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4018,38 +4018,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1209</v>
+        <v>4368</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657086</v>
+        <v>657148</v>
       </c>
       <c r="R31" t="n">
-        <v>7004011</v>
+        <v>7003847</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4081,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4106,12 +4106,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 20398-2024 artfynd.xlsx
+++ b/artfynd/A 20398-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119524674</v>
+        <v>119525850</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Ysjön, Stor-Ysjön, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>656455</v>
+        <v>657183</v>
       </c>
       <c r="R2" t="n">
-        <v>7003293</v>
+        <v>7003552</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119527476</v>
+        <v>119525973</v>
       </c>
       <c r="B3" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>657111</v>
+        <v>657195</v>
       </c>
       <c r="R3" t="n">
-        <v>7003979</v>
+        <v>7003530</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119527379</v>
+        <v>119527526</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>657184</v>
+        <v>657104</v>
       </c>
       <c r="R4" t="n">
-        <v>7003931</v>
+        <v>7004039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119528299</v>
+        <v>119528058</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,16 +1037,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,24 +1055,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>656947</v>
+        <v>657136</v>
       </c>
       <c r="R5" t="n">
-        <v>7003654</v>
+        <v>7003879</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119527975</v>
+        <v>119528534</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,39 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>657086</v>
+        <v>656805</v>
       </c>
       <c r="R6" t="n">
-        <v>7003964</v>
+        <v>7003583</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1250,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119528382</v>
+        <v>119523535</v>
       </c>
       <c r="B7" t="n">
         <v>57310</v>
@@ -1291,14 +1291,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>656799</v>
+        <v>656823</v>
       </c>
       <c r="R7" t="n">
-        <v>7003637</v>
+        <v>7003493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,19 +1355,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119528058</v>
+        <v>119527614</v>
       </c>
       <c r="B8" t="n">
         <v>57310</v>
@@ -1401,16 +1401,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>657136</v>
+        <v>657068</v>
       </c>
       <c r="R8" t="n">
-        <v>7003879</v>
+        <v>7004042</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1447,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,12 +1457,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:03</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119526215</v>
+        <v>119524501</v>
       </c>
       <c r="B9" t="n">
-        <v>97928</v>
+        <v>97907</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,41 +1496,50 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>657282</v>
+        <v>656721</v>
       </c>
       <c r="R9" t="n">
-        <v>7003488</v>
+        <v>7003352</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,7 +1568,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1578,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,22 +1593,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119526406</v>
+        <v>119525210</v>
       </c>
       <c r="B10" t="n">
-        <v>90846</v>
+        <v>100171</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,38 +1617,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>222498</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>657317</v>
+        <v>656894</v>
       </c>
       <c r="R10" t="n">
-        <v>7003487</v>
+        <v>7003417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1671,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1681,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1696,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119525652</v>
+        <v>119528299</v>
       </c>
       <c r="B11" t="n">
-        <v>97806</v>
+        <v>57326</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1720,41 +1729,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219795</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>657169</v>
+        <v>656947</v>
       </c>
       <c r="R11" t="n">
-        <v>7003646</v>
+        <v>7003654</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1793,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,22 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119523873</v>
+        <v>119527975</v>
       </c>
       <c r="B12" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1832,38 +1846,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>656603</v>
+        <v>657086</v>
       </c>
       <c r="R12" t="n">
-        <v>7003380</v>
+        <v>7003964</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1905,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1932,10 +1951,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119525973</v>
+        <v>119527172</v>
       </c>
       <c r="B13" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,16 +1967,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1966,21 +1985,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>657195</v>
+        <v>657236</v>
       </c>
       <c r="R13" t="n">
-        <v>7003530</v>
+        <v>7003883</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2012,7 +2026,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2036,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:24</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,10 +2068,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119524501</v>
+        <v>119526277</v>
       </c>
       <c r="B14" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2061,47 +2080,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>656721</v>
+        <v>657328</v>
       </c>
       <c r="R14" t="n">
-        <v>7003352</v>
+        <v>7003543</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2133,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2158,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119527309</v>
+        <v>119525839</v>
       </c>
       <c r="B15" t="n">
         <v>57310</v>
@@ -2204,26 +2219,21 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>657217</v>
+        <v>657171</v>
       </c>
       <c r="R15" t="n">
-        <v>7003868</v>
+        <v>7003519</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2265,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2265,7 +2275,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,22 +2290,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119524730</v>
+        <v>119528084</v>
       </c>
       <c r="B16" t="n">
-        <v>57463</v>
+        <v>91858</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2308,43 +2318,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>4368</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>656817</v>
+        <v>657148</v>
       </c>
       <c r="R16" t="n">
-        <v>7003454</v>
+        <v>7003847</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2376,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2386,7 +2387,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:11</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,19 +2402,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119525210</v>
+        <v>119523806</v>
       </c>
       <c r="B17" t="n">
         <v>100171</v>
@@ -2453,10 +2454,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656894</v>
+        <v>656688</v>
       </c>
       <c r="R17" t="n">
-        <v>7003417</v>
+        <v>7003344</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2488,7 +2489,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2498,7 +2499,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2525,10 +2526,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119525839</v>
+        <v>119527722</v>
       </c>
       <c r="B18" t="n">
-        <v>57310</v>
+        <v>90562</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,39 +2542,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657171</v>
+        <v>657093</v>
       </c>
       <c r="R18" t="n">
-        <v>7003519</v>
+        <v>7004017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2605,7 +2601,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2615,7 +2611,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2642,10 +2638,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119528005</v>
+        <v>119528550</v>
       </c>
       <c r="B19" t="n">
-        <v>90752</v>
+        <v>57463</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,41 +2650,50 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>657098</v>
+        <v>656801</v>
       </c>
       <c r="R19" t="n">
-        <v>7003930</v>
+        <v>7003583</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2727,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2754,10 +2759,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>119523532</v>
+        <v>119523624</v>
       </c>
       <c r="B20" t="n">
-        <v>57310</v>
+        <v>100171</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2766,43 +2771,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>656779</v>
+        <v>656721</v>
       </c>
       <c r="R20" t="n">
-        <v>7003525</v>
+        <v>7003352</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2834,7 +2834,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2871,10 +2871,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>119528488</v>
+        <v>119528213</v>
       </c>
       <c r="B21" t="n">
-        <v>57310</v>
+        <v>57326</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,16 +2887,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2905,16 +2905,21 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>656794</v>
+        <v>657029</v>
       </c>
       <c r="R21" t="n">
-        <v>7003590</v>
+        <v>7003715</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2946,7 +2951,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:37</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2956,12 +2961,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:37</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,10 +2988,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119525842</v>
+        <v>119527302</v>
       </c>
       <c r="B22" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3000,41 +3000,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>657255</v>
+        <v>657209</v>
       </c>
       <c r="R22" t="n">
-        <v>7003601</v>
+        <v>7003883</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3063,7 +3063,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3073,7 +3073,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3088,22 +3093,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119526344</v>
+        <v>119527359</v>
       </c>
       <c r="B23" t="n">
-        <v>96868</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3112,38 +3117,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>657297</v>
+        <v>657182</v>
       </c>
       <c r="R23" t="n">
-        <v>7003492</v>
+        <v>7003902</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3175,7 +3180,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3185,7 +3190,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,10 +3217,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119527722</v>
+        <v>119525206</v>
       </c>
       <c r="B24" t="n">
-        <v>90562</v>
+        <v>91832</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3228,34 +3233,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>657093</v>
+        <v>656891</v>
       </c>
       <c r="R24" t="n">
-        <v>7004017</v>
+        <v>7003421</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3287,7 +3292,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3297,7 +3302,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119528534</v>
+        <v>119523873</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>100171</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3336,25 +3341,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3364,10 +3369,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>656805</v>
+        <v>656603</v>
       </c>
       <c r="R25" t="n">
-        <v>7003583</v>
+        <v>7003380</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3399,7 +3404,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3409,7 +3414,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3436,10 +3441,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119527614</v>
+        <v>119525652</v>
       </c>
       <c r="B26" t="n">
-        <v>57310</v>
+        <v>97806</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3448,43 +3453,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>219795</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>657068</v>
+        <v>657169</v>
       </c>
       <c r="R26" t="n">
-        <v>7004042</v>
+        <v>7003646</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3541,22 +3541,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119523806</v>
+        <v>119528347</v>
       </c>
       <c r="B27" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3565,38 +3565,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>656688</v>
+        <v>656839</v>
       </c>
       <c r="R27" t="n">
-        <v>7003344</v>
+        <v>7003637</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3628,7 +3633,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3638,7 +3643,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3665,10 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119528244</v>
+        <v>119525856</v>
       </c>
       <c r="B28" t="n">
-        <v>100171</v>
+        <v>57310</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3677,38 +3682,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222498</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>656999</v>
+        <v>657237</v>
       </c>
       <c r="R28" t="n">
-        <v>7003725</v>
+        <v>7003595</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3740,7 +3750,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3750,7 +3760,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3765,19 +3775,19 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119527959</v>
+        <v>119528382</v>
       </c>
       <c r="B29" t="n">
         <v>57310</v>
@@ -3811,16 +3821,21 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>657090</v>
+        <v>656799</v>
       </c>
       <c r="R29" t="n">
-        <v>7003971</v>
+        <v>7003637</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3852,7 +3867,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3862,12 +3877,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:57</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3894,10 +3904,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119527794</v>
+        <v>119526215</v>
       </c>
       <c r="B30" t="n">
-        <v>91005</v>
+        <v>97928</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3906,38 +3916,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>657086</v>
+        <v>657282</v>
       </c>
       <c r="R30" t="n">
-        <v>7004011</v>
+        <v>7003488</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3969,7 +3979,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3979,7 +3989,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4006,10 +4016,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119528084</v>
+        <v>119528488</v>
       </c>
       <c r="B31" t="n">
-        <v>91858</v>
+        <v>57310</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4022,34 +4032,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4368</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>657148</v>
+        <v>656794</v>
       </c>
       <c r="R31" t="n">
-        <v>7003847</v>
+        <v>7003590</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4081,7 +4091,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:37</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4091,7 +4101,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>18:37</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4118,7 +4133,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119523535</v>
+        <v>119524674</v>
       </c>
       <c r="B32" t="n">
         <v>57310</v>
@@ -4159,17 +4174,17 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Stor-Ysjön, Stor-Ysjön, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>656823</v>
+        <v>656455</v>
       </c>
       <c r="R32" t="n">
-        <v>7003493</v>
+        <v>7003293</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4198,7 +4213,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4208,7 +4223,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4235,7 +4250,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119527526</v>
+        <v>119523532</v>
       </c>
       <c r="B33" t="n">
         <v>57310</v>
@@ -4269,19 +4284,24 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>657104</v>
+        <v>656779</v>
       </c>
       <c r="R33" t="n">
-        <v>7004039</v>
+        <v>7003525</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4310,7 +4330,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4320,12 +4340,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4340,19 +4355,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119527172</v>
+        <v>119527959</v>
       </c>
       <c r="B34" t="n">
         <v>57310</v>
@@ -4392,10 +4407,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>657236</v>
+        <v>657090</v>
       </c>
       <c r="R34" t="n">
-        <v>7003883</v>
+        <v>7003971</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4427,7 +4442,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4437,7 +4452,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
@@ -4457,22 +4472,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119525850</v>
+        <v>119526344</v>
       </c>
       <c r="B35" t="n">
-        <v>100171</v>
+        <v>96868</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4485,21 +4500,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>222498</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4509,10 +4524,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>657183</v>
+        <v>657297</v>
       </c>
       <c r="R35" t="n">
-        <v>7003552</v>
+        <v>7003492</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4544,7 +4559,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4554,7 +4569,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4569,22 +4584,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119528213</v>
+        <v>119527379</v>
       </c>
       <c r="B36" t="n">
-        <v>57326</v>
+        <v>90527</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4593,43 +4608,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>657029</v>
+        <v>657184</v>
       </c>
       <c r="R36" t="n">
-        <v>7003715</v>
+        <v>7003931</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4661,7 +4671,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4671,7 +4681,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4686,19 +4696,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119528347</v>
+        <v>119527567</v>
       </c>
       <c r="B37" t="n">
         <v>57310</v>
@@ -4732,21 +4742,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>656839</v>
+        <v>657075</v>
       </c>
       <c r="R37" t="n">
-        <v>7003637</v>
+        <v>7004045</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4778,7 +4783,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4788,7 +4793,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4815,10 +4825,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119526277</v>
+        <v>119525443</v>
       </c>
       <c r="B38" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4827,31 +4837,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4860,13 +4869,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>657328</v>
+        <v>657092</v>
       </c>
       <c r="R38" t="n">
-        <v>7003543</v>
+        <v>7003598</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4895,7 +4904,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4905,7 +4914,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4920,22 +4929,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119525443</v>
+        <v>119527794</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>91005</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4948,38 +4957,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>657092</v>
+        <v>657086</v>
       </c>
       <c r="R39" t="n">
-        <v>7003598</v>
+        <v>7004011</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5011,7 +5016,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5021,7 +5026,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5048,10 +5053,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119527359</v>
+        <v>119527476</v>
       </c>
       <c r="B40" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5064,21 +5069,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5088,10 +5093,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>657182</v>
+        <v>657111</v>
       </c>
       <c r="R40" t="n">
-        <v>7003902</v>
+        <v>7003979</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5123,7 +5128,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5133,7 +5138,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5160,7 +5165,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119525856</v>
+        <v>119527309</v>
       </c>
       <c r="B41" t="n">
         <v>57310</v>
@@ -5194,21 +5199,26 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>657237</v>
+        <v>657217</v>
       </c>
       <c r="R41" t="n">
-        <v>7003595</v>
+        <v>7003868</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5240,7 +5250,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5250,7 +5260,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5277,10 +5287,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119527302</v>
+        <v>119525842</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>100171</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5289,41 +5299,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>657209</v>
+        <v>657255</v>
       </c>
       <c r="R42" t="n">
-        <v>7003883</v>
+        <v>7003601</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5352,7 +5362,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5362,12 +5372,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:25</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5382,22 +5387,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119527567</v>
+        <v>119526406</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>90846</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5410,34 +5415,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>657075</v>
+        <v>657317</v>
       </c>
       <c r="R43" t="n">
-        <v>7004045</v>
+        <v>7003487</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5469,7 +5474,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5479,12 +5484,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5499,22 +5499,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119528550</v>
+        <v>119528244</v>
       </c>
       <c r="B44" t="n">
-        <v>57463</v>
+        <v>100171</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5523,50 +5523,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>222498</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>656801</v>
+        <v>656999</v>
       </c>
       <c r="R44" t="n">
-        <v>7003583</v>
+        <v>7003725</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5595,7 +5586,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5605,7 +5596,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5632,10 +5623,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119525206</v>
+        <v>119528005</v>
       </c>
       <c r="B45" t="n">
-        <v>91832</v>
+        <v>90752</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5644,38 +5635,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4361</v>
+        <v>48</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>656891</v>
+        <v>657098</v>
       </c>
       <c r="R45" t="n">
-        <v>7003421</v>
+        <v>7003930</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5707,7 +5698,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5717,7 +5708,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5744,10 +5735,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119523624</v>
+        <v>119524730</v>
       </c>
       <c r="B46" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5756,41 +5747,50 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>656721</v>
+        <v>656817</v>
       </c>
       <c r="R46" t="n">
-        <v>7003352</v>
+        <v>7003454</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5829,7 +5829,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5844,12 +5844,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>

--- a/artfynd/A 20398-2024 artfynd.xlsx
+++ b/artfynd/A 20398-2024 artfynd.xlsx
@@ -1605,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119525210</v>
+        <v>119528299</v>
       </c>
       <c r="B10" t="n">
-        <v>100171</v>
+        <v>57326</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1617,41 +1617,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>656894</v>
+        <v>656947</v>
       </c>
       <c r="R10" t="n">
-        <v>7003417</v>
+        <v>7003654</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1680,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119528299</v>
+        <v>119527975</v>
       </c>
       <c r="B11" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,16 +1738,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1753,22 +1758,22 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>656947</v>
+        <v>657086</v>
       </c>
       <c r="R11" t="n">
-        <v>7003654</v>
+        <v>7003964</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1834,10 +1839,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119527975</v>
+        <v>119525210</v>
       </c>
       <c r="B12" t="n">
-        <v>57310</v>
+        <v>100171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1846,43 +1851,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>657086</v>
+        <v>656894</v>
       </c>
       <c r="R12" t="n">
-        <v>7003964</v>
+        <v>7003417</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119523806</v>
+        <v>119528550</v>
       </c>
       <c r="B17" t="n">
-        <v>100171</v>
+        <v>57463</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2426,41 +2426,50 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
+          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>656688</v>
+        <v>656801</v>
       </c>
       <c r="R17" t="n">
-        <v>7003344</v>
+        <v>7003583</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2489,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2499,7 +2508,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2526,10 +2535,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>119527722</v>
+        <v>119523806</v>
       </c>
       <c r="B18" t="n">
-        <v>90562</v>
+        <v>100171</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2538,38 +2547,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lill-Lomtjärnen, Lill-Lomtjärnen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>657093</v>
+        <v>656688</v>
       </c>
       <c r="R18" t="n">
-        <v>7004017</v>
+        <v>7003344</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2601,7 +2610,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2611,7 +2620,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2638,10 +2647,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>119528550</v>
+        <v>119527722</v>
       </c>
       <c r="B19" t="n">
-        <v>57463</v>
+        <v>90562</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2654,46 +2663,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Kvarntjärnen, Kvarntjärnen, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>656801</v>
+        <v>657093</v>
       </c>
       <c r="R19" t="n">
-        <v>7003583</v>
+        <v>7004017</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4596,10 +4596,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119527379</v>
+        <v>119525443</v>
       </c>
       <c r="B36" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4608,38 +4608,42 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
+          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>657184</v>
+        <v>657092</v>
       </c>
       <c r="R36" t="n">
-        <v>7003931</v>
+        <v>7003598</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4671,7 +4675,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4681,7 +4685,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4708,10 +4712,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119527567</v>
+        <v>119527379</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>90527</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4720,25 +4724,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4748,10 +4752,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>657075</v>
+        <v>657184</v>
       </c>
       <c r="R37" t="n">
-        <v>7004045</v>
+        <v>7003931</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4783,7 +4787,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4793,12 +4797,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:41</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4813,22 +4812,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119525443</v>
+        <v>119527567</v>
       </c>
       <c r="B38" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4837,42 +4836,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lomtjärnshöjden, Lomtjärnshöjden, Ång</t>
+          <t>Djuptjärnshöjden, Djuptjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>657092</v>
+        <v>657075</v>
       </c>
       <c r="R38" t="n">
-        <v>7003598</v>
+        <v>7004045</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4904,7 +4899,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4914,7 +4909,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:44</t>
+          <t>17:41</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4929,12 +4929,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
